--- a/dist/tally_templates/DJCF.xlsx
+++ b/dist/tally_templates/DJCF.xlsx
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -3015,7 +3015,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="622">
+  <cellXfs count="662">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4848,6 +4848,126 @@
     <xf numFmtId="170" fontId="8" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4855,11 +4975,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5176,7 +5296,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y139"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -5930,9 +6050,7 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>144</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
@@ -5985,7 +6103,7 @@
       <c r="G8" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="372" t="s">
+      <c r="H8" s="661" t="s">
         <v>147</v>
       </c>
       <c r="I8" s="372"/>
@@ -7287,9 +7405,7 @@
       <c r="Y54" s="3"/>
     </row>
     <row r="55" hidden="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>144</v>
-      </c>
+      <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
@@ -7334,14 +7450,14 @@
       <c r="D56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="175">
+      <c r="E56" s="190">
         <v>7</v>
       </c>
       <c r="F56" s="175"/>
       <c r="G56" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="H56" s="372" t="s">
+      <c r="H56" s="661" t="s">
         <v>147</v>
       </c>
       <c r="I56" s="372"/>
@@ -8520,9 +8636,7 @@
       <c r="Y97" s="1"/>
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
-        <v>144</v>
-      </c>
+      <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3" t="s">
@@ -8575,7 +8689,7 @@
       <c r="G99" s="319" t="s">
         <v>8</v>
       </c>
-      <c r="H99" s="372" t="s">
+      <c r="H99" s="661" t="s">
         <v>147</v>
       </c>
       <c r="I99" s="372"/>
@@ -8700,27 +8814,17 @@
       <c r="Y102" s="1"/>
     </row>
     <row r="103" ht="21" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A103" s="440" t="s">
-        <v>166</v>
-      </c>
+      <c r="A103" s="440"/>
       <c r="B103" s="441"/>
-      <c r="C103" s="413" t="s">
-        <v>167</v>
-      </c>
+      <c r="C103" s="413"/>
       <c r="D103" s="252"/>
       <c r="E103" s="252"/>
-      <c r="F103" s="442">
-        <v>-18</v>
-      </c>
-      <c r="G103" s="442">
-        <v>-11.4</v>
-      </c>
+      <c r="F103" s="442"/>
+      <c r="G103" s="442"/>
       <c r="H103" s="425" t="s">
         <v>168</v>
       </c>
-      <c r="I103" s="443" t="s">
-        <v>169</v>
-      </c>
+      <c r="I103" s="443"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -9832,7 +9936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -10562,7 +10666,7 @@
       <c r="A6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="190" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -10574,7 +10678,7 @@
       <c r="I6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="639"/>
       <c r="K6" s="3" t="str">
         <f>'OS-OUT'!H6</f>
         <v>0149S</v>
@@ -10630,7 +10734,7 @@
       <c r="A8" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="188" t="s">
+      <c r="B8" s="190" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="188"/>
@@ -10691,7 +10795,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="193" t="s">
         <v>11</v>
       </c>
@@ -10732,7 +10836,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="196"/>
       <c r="B11" s="196"/>
       <c r="C11" s="249"/>
@@ -11542,7 +11646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -11838,7 +11942,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -11898,7 +12002,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="622" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -11907,13 +12011,13 @@
       <c r="F4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="623"/>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
       <c r="J4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="624"/>
       <c r="L4" s="12"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
@@ -11960,20 +12064,20 @@
       <c r="A6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="623"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="623"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="17"/>
+      <c r="K6" s="625"/>
       <c r="L6" s="18" t="s">
         <v>9</v>
       </c>
@@ -14803,7 +14907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -15458,7 +15562,7 @@
       <c r="A6" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="40"/>
+      <c r="B6" s="653"/>
       <c r="C6" s="40"/>
       <c r="D6" s="241" t="s">
         <v>3</v>
@@ -15476,7 +15580,7 @@
       <c r="O6" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="P6" s="40"/>
+      <c r="P6" s="653"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="145" t="str">
         <f>'Final Work'!G4</f>
@@ -15546,7 +15650,7 @@
       <c r="A8" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="138"/>
+      <c r="B8" s="655"/>
       <c r="C8" s="138"/>
       <c r="D8" s="296" t="s">
         <v>174</v>
@@ -15564,7 +15668,7 @@
       <c r="O8" s="296" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="138"/>
+      <c r="P8" s="655"/>
       <c r="Q8" s="138"/>
       <c r="R8" s="297">
         <f>'Final Work'!G6</f>
@@ -15581,7 +15685,7 @@
       </c>
       <c r="Z8" s="297"/>
       <c r="AA8" s="297"/>
-      <c r="AB8" s="297" t="s">
+      <c r="AB8" s="655" t="s">
         <v>26</v>
       </c>
       <c r="AC8" s="297"/>
@@ -21149,7 +21253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -21789,7 +21893,7 @@
       <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="142" t="s">
+      <c r="B5" s="626" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="142"/>
@@ -21851,7 +21955,7 @@
       <c r="A7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="143" t="s">
+      <c r="B7" s="627" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="144"/>
@@ -21866,7 +21970,7 @@
       <c r="G7" s="145" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="626" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="9"/>
@@ -22006,7 +22110,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="150"/>
-      <c r="C12" s="151"/>
+      <c r="C12" s="628"/>
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -22033,7 +22137,7 @@
     <row r="13" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="152"/>
       <c r="B13" s="153"/>
-      <c r="C13" s="154"/>
+      <c r="C13" s="629"/>
       <c r="D13" s="154"/>
       <c r="E13" s="154"/>
       <c r="F13" s="154"/>
@@ -22060,7 +22164,7 @@
     <row r="14" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="152"/>
       <c r="B14" s="155"/>
-      <c r="C14" s="156"/>
+      <c r="C14" s="630"/>
       <c r="D14" s="157"/>
       <c r="E14" s="157"/>
       <c r="F14" s="157"/>
@@ -22087,7 +22191,7 @@
     <row r="15" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="152"/>
       <c r="B15" s="155"/>
-      <c r="C15" s="156"/>
+      <c r="C15" s="630"/>
       <c r="D15" s="157"/>
       <c r="E15" s="157"/>
       <c r="F15" s="157"/>
@@ -22114,7 +22218,7 @@
     <row r="16" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="159"/>
       <c r="B16" s="160"/>
-      <c r="C16" s="161"/>
+      <c r="C16" s="631"/>
       <c r="D16" s="162"/>
       <c r="E16" s="162"/>
       <c r="F16" s="162"/>
@@ -22141,7 +22245,7 @@
     <row r="17" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="164"/>
       <c r="B17" s="165"/>
-      <c r="C17" s="166"/>
+      <c r="C17" s="632"/>
       <c r="D17" s="167"/>
       <c r="E17" s="167"/>
       <c r="F17" s="167"/>
@@ -22168,7 +22272,7 @@
     <row r="18" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="169"/>
       <c r="B18" s="165"/>
-      <c r="C18" s="156"/>
+      <c r="C18" s="630"/>
       <c r="D18" s="157"/>
       <c r="E18" s="157"/>
       <c r="F18" s="157"/>
@@ -22197,7 +22301,7 @@
     <row r="19" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="170"/>
       <c r="B19" s="155"/>
-      <c r="C19" s="156"/>
+      <c r="C19" s="630"/>
       <c r="D19" s="157"/>
       <c r="E19" s="157"/>
       <c r="F19" s="157"/>
@@ -22224,7 +22328,7 @@
     <row r="20" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="170"/>
       <c r="B20" s="165"/>
-      <c r="C20" s="166"/>
+      <c r="C20" s="632"/>
       <c r="D20" s="167"/>
       <c r="E20" s="167"/>
       <c r="F20" s="167"/>
@@ -22251,7 +22355,7 @@
     <row r="21" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="159"/>
       <c r="B21" s="160"/>
-      <c r="C21" s="161"/>
+      <c r="C21" s="631"/>
       <c r="D21" s="162"/>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -22278,7 +22382,7 @@
     <row r="22" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="29"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="171"/>
+      <c r="C22" s="633"/>
       <c r="D22" s="172"/>
       <c r="E22" s="172"/>
       <c r="F22" s="172"/>
@@ -22305,7 +22409,7 @@
     <row r="23" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="169"/>
       <c r="B23" s="165"/>
-      <c r="C23" s="174"/>
+      <c r="C23" s="634"/>
       <c r="D23" s="174"/>
       <c r="E23" s="174"/>
       <c r="F23" s="174"/>
@@ -22332,7 +22436,7 @@
     <row r="24" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="164"/>
       <c r="B24" s="165"/>
-      <c r="C24" s="166"/>
+      <c r="C24" s="632"/>
       <c r="D24" s="167"/>
       <c r="E24" s="167"/>
       <c r="F24" s="167"/>
@@ -22359,7 +22463,7 @@
     <row r="25" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="170"/>
       <c r="B25" s="165"/>
-      <c r="C25" s="166"/>
+      <c r="C25" s="632"/>
       <c r="D25" s="167"/>
       <c r="E25" s="167"/>
       <c r="F25" s="167"/>
@@ -22386,7 +22490,7 @@
     <row r="26" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="159"/>
       <c r="B26" s="160"/>
-      <c r="C26" s="161"/>
+      <c r="C26" s="631"/>
       <c r="D26" s="162"/>
       <c r="E26" s="162"/>
       <c r="F26" s="162"/>
@@ -22413,7 +22517,7 @@
     <row r="27" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="164"/>
       <c r="B27" s="155"/>
-      <c r="C27" s="156"/>
+      <c r="C27" s="630"/>
       <c r="D27" s="157"/>
       <c r="E27" s="157"/>
       <c r="F27" s="157"/>
@@ -22440,7 +22544,7 @@
     <row r="28" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="164"/>
       <c r="B28" s="165"/>
-      <c r="C28" s="166"/>
+      <c r="C28" s="632"/>
       <c r="D28" s="167"/>
       <c r="E28" s="167"/>
       <c r="F28" s="167"/>
@@ -22467,7 +22571,7 @@
     <row r="29" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="170"/>
       <c r="B29" s="165"/>
-      <c r="C29" s="174"/>
+      <c r="C29" s="634"/>
       <c r="D29" s="174"/>
       <c r="E29" s="174"/>
       <c r="F29" s="174"/>
@@ -22494,7 +22598,7 @@
     <row r="30" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="176"/>
       <c r="B30" s="155"/>
-      <c r="C30" s="156"/>
+      <c r="C30" s="630"/>
       <c r="D30" s="157"/>
       <c r="E30" s="157"/>
       <c r="F30" s="157"/>
@@ -22521,7 +22625,7 @@
     <row r="31" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="159"/>
       <c r="B31" s="160"/>
-      <c r="C31" s="161"/>
+      <c r="C31" s="631"/>
       <c r="D31" s="162"/>
       <c r="E31" s="162"/>
       <c r="F31" s="162"/>
@@ -22548,7 +22652,7 @@
     <row r="32" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="29"/>
       <c r="B32" s="165"/>
-      <c r="C32" s="166"/>
+      <c r="C32" s="632"/>
       <c r="D32" s="167"/>
       <c r="E32" s="167"/>
       <c r="F32" s="167"/>
@@ -22575,7 +22679,7 @@
     <row r="33" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="170"/>
       <c r="B33" s="165"/>
-      <c r="C33" s="166"/>
+      <c r="C33" s="632"/>
       <c r="D33" s="167"/>
       <c r="E33" s="167"/>
       <c r="F33" s="167"/>
@@ -22602,7 +22706,7 @@
     <row r="34" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="152"/>
       <c r="B34" s="165"/>
-      <c r="C34" s="174"/>
+      <c r="C34" s="634"/>
       <c r="D34" s="174"/>
       <c r="E34" s="174"/>
       <c r="F34" s="174"/>
@@ -22629,7 +22733,7 @@
     <row r="35" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="176"/>
       <c r="B35" s="155"/>
-      <c r="C35" s="156"/>
+      <c r="C35" s="630"/>
       <c r="D35" s="157"/>
       <c r="E35" s="157"/>
       <c r="F35" s="157"/>
@@ -22654,9 +22758,9 @@
       <c r="Y35" s="3"/>
     </row>
     <row r="36" ht="17.7" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A36" s="177"/>
+      <c r="A36" s="635"/>
       <c r="B36" s="178"/>
-      <c r="C36" s="179"/>
+      <c r="C36" s="636"/>
       <c r="D36" s="180"/>
       <c r="E36" s="180"/>
       <c r="F36" s="180"/>
@@ -22683,7 +22787,7 @@
     <row r="37" ht="17.7" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="29"/>
       <c r="B37" s="165"/>
-      <c r="C37" s="166"/>
+      <c r="C37" s="632"/>
       <c r="D37" s="167"/>
       <c r="E37" s="167"/>
       <c r="F37" s="167"/>
@@ -22710,7 +22814,7 @@
     <row r="38" ht="17.7" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="170"/>
       <c r="B38" s="155"/>
-      <c r="C38" s="156"/>
+      <c r="C38" s="630"/>
       <c r="D38" s="157"/>
       <c r="E38" s="157"/>
       <c r="F38" s="157"/>
@@ -22737,7 +22841,7 @@
     <row r="39" ht="17.7" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="152"/>
       <c r="B39" s="155"/>
-      <c r="C39" s="156"/>
+      <c r="C39" s="630"/>
       <c r="D39" s="157"/>
       <c r="E39" s="157"/>
       <c r="F39" s="157"/>
@@ -22764,7 +22868,7 @@
     <row r="40" ht="17.7" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="176"/>
       <c r="B40" s="155"/>
-      <c r="C40" s="156"/>
+      <c r="C40" s="630"/>
       <c r="D40" s="157"/>
       <c r="E40" s="157"/>
       <c r="F40" s="157"/>
@@ -22789,9 +22893,9 @@
       <c r="Y40" s="3"/>
     </row>
     <row r="41" ht="17.7" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="177"/>
+      <c r="A41" s="635"/>
       <c r="B41" s="160"/>
-      <c r="C41" s="182"/>
+      <c r="C41" s="637"/>
       <c r="D41" s="182"/>
       <c r="E41" s="182"/>
       <c r="F41" s="182"/>
@@ -23088,7 +23192,7 @@
       <c r="Y51" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="41">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -23127,6 +23231,9 @@
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.31496062992125984" footer="0.35433070866141736"/>
@@ -23135,7 +23242,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -23930,7 +24037,7 @@
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="190" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -23940,13 +24047,13 @@
       <c r="G6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="175"/>
+      <c r="H6" s="190"/>
       <c r="I6" s="175"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="189"/>
+      <c r="L6" s="638"/>
       <c r="M6" s="175"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -23992,7 +24099,7 @@
       <c r="A8" s="188" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="639" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="3"/>
@@ -24002,13 +24109,13 @@
       <c r="G8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="175"/>
+      <c r="H8" s="190"/>
       <c r="I8" s="175"/>
       <c r="J8" s="3"/>
       <c r="K8" s="188" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="175"/>
+      <c r="L8" s="190"/>
       <c r="M8" s="175"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -24050,7 +24157,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="191" t="s">
         <v>48</v>
       </c>
@@ -24095,7 +24202,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="194"/>
       <c r="B11" s="195"/>
       <c r="C11" s="195"/>
@@ -24125,19 +24232,19 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="197"/>
+      <c r="A12" s="640"/>
       <c r="B12" s="198"/>
       <c r="C12" s="199"/>
-      <c r="D12" s="200"/>
-      <c r="E12" s="201"/>
-      <c r="F12" s="202"/>
+      <c r="D12" s="641"/>
+      <c r="E12" s="642"/>
+      <c r="F12" s="643"/>
       <c r="G12" s="203"/>
       <c r="H12" s="204"/>
       <c r="I12" s="205"/>
       <c r="J12" s="206"/>
       <c r="K12" s="203"/>
       <c r="L12" s="203"/>
-      <c r="M12" s="207"/>
+      <c r="M12" s="50"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -24152,19 +24259,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="197"/>
+      <c r="A13" s="640"/>
       <c r="B13" s="208"/>
       <c r="C13" s="208"/>
-      <c r="D13" s="200"/>
-      <c r="E13" s="201"/>
-      <c r="F13" s="202"/>
+      <c r="D13" s="641"/>
+      <c r="E13" s="642"/>
+      <c r="F13" s="643"/>
       <c r="G13" s="203"/>
       <c r="H13" s="209"/>
       <c r="I13" s="210"/>
       <c r="J13" s="206"/>
       <c r="K13" s="203"/>
       <c r="L13" s="203"/>
-      <c r="M13" s="207"/>
+      <c r="M13" s="50"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -24179,19 +24286,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="197"/>
+      <c r="A14" s="640"/>
       <c r="B14" s="198"/>
       <c r="C14" s="199"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="201"/>
-      <c r="F14" s="202"/>
+      <c r="D14" s="641"/>
+      <c r="E14" s="642"/>
+      <c r="F14" s="643"/>
       <c r="G14" s="203"/>
       <c r="H14" s="204"/>
       <c r="I14" s="205"/>
       <c r="J14" s="206"/>
       <c r="K14" s="203"/>
       <c r="L14" s="203"/>
-      <c r="M14" s="207"/>
+      <c r="M14" s="50"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -24206,19 +24313,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="211"/>
+      <c r="A15" s="644"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
-      <c r="D15" s="200"/>
-      <c r="E15" s="201"/>
-      <c r="F15" s="202"/>
+      <c r="D15" s="641"/>
+      <c r="E15" s="642"/>
+      <c r="F15" s="643"/>
       <c r="G15" s="203"/>
       <c r="H15" s="209"/>
       <c r="I15" s="210"/>
       <c r="J15" s="206"/>
       <c r="K15" s="203"/>
       <c r="L15" s="203"/>
-      <c r="M15" s="207"/>
+      <c r="M15" s="50"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -24233,19 +24340,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="211"/>
+      <c r="A16" s="644"/>
       <c r="B16" s="198"/>
       <c r="C16" s="199"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="201"/>
-      <c r="F16" s="202"/>
+      <c r="D16" s="641"/>
+      <c r="E16" s="642"/>
+      <c r="F16" s="643"/>
       <c r="G16" s="203"/>
       <c r="H16" s="204"/>
       <c r="I16" s="205"/>
       <c r="J16" s="206"/>
       <c r="K16" s="203"/>
       <c r="L16" s="203"/>
-      <c r="M16" s="207"/>
+      <c r="M16" s="50"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -24260,19 +24367,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="211"/>
+      <c r="A17" s="644"/>
       <c r="B17" s="208"/>
       <c r="C17" s="208"/>
-      <c r="D17" s="212"/>
-      <c r="E17" s="213"/>
-      <c r="F17" s="214"/>
+      <c r="D17" s="645"/>
+      <c r="E17" s="646"/>
+      <c r="F17" s="647"/>
       <c r="G17" s="208"/>
       <c r="H17" s="215"/>
       <c r="I17" s="216"/>
       <c r="J17" s="215"/>
       <c r="K17" s="208"/>
       <c r="L17" s="208"/>
-      <c r="M17" s="217"/>
+      <c r="M17" s="61"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -24287,19 +24394,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="211"/>
+      <c r="A18" s="644"/>
       <c r="B18" s="208"/>
       <c r="C18" s="208"/>
-      <c r="D18" s="212"/>
-      <c r="E18" s="213"/>
-      <c r="F18" s="214"/>
+      <c r="D18" s="645"/>
+      <c r="E18" s="646"/>
+      <c r="F18" s="647"/>
       <c r="G18" s="208"/>
       <c r="H18" s="215"/>
       <c r="I18" s="216"/>
       <c r="J18" s="215"/>
       <c r="K18" s="208"/>
       <c r="L18" s="208"/>
-      <c r="M18" s="218"/>
+      <c r="M18" s="648"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -24314,19 +24421,19 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="211"/>
+      <c r="A19" s="644"/>
       <c r="B19" s="208"/>
       <c r="C19" s="208"/>
-      <c r="D19" s="212"/>
-      <c r="E19" s="213"/>
-      <c r="F19" s="214"/>
+      <c r="D19" s="645"/>
+      <c r="E19" s="646"/>
+      <c r="F19" s="647"/>
       <c r="G19" s="208"/>
       <c r="H19" s="215"/>
       <c r="I19" s="216"/>
       <c r="J19" s="215"/>
       <c r="K19" s="208"/>
       <c r="L19" s="208"/>
-      <c r="M19" s="217"/>
+      <c r="M19" s="61"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -24734,7 +24841,7 @@
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
     </row>
-    <row r="34" ht="12.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="184" t="s">
         <v>23</v>
       </c>
@@ -24947,7 +25054,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -25741,7 +25848,7 @@
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="190" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -25751,13 +25858,13 @@
       <c r="G6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="175"/>
+      <c r="H6" s="190"/>
       <c r="I6" s="175"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="189"/>
+      <c r="L6" s="638"/>
       <c r="M6" s="175"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -25803,7 +25910,7 @@
       <c r="A8" s="188" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="639" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="267"/>
@@ -25813,13 +25920,13 @@
       <c r="G8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="175"/>
+      <c r="H8" s="190"/>
       <c r="I8" s="175"/>
       <c r="J8" s="3"/>
       <c r="K8" s="188" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="175"/>
+      <c r="L8" s="190"/>
       <c r="M8" s="175"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -25936,19 +26043,19 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="197"/>
+      <c r="A12" s="640"/>
       <c r="B12" s="268"/>
       <c r="C12" s="269"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="214"/>
+      <c r="D12" s="645"/>
+      <c r="E12" s="646"/>
+      <c r="F12" s="647"/>
       <c r="G12" s="208"/>
       <c r="H12" s="215"/>
       <c r="I12" s="216"/>
       <c r="J12" s="215"/>
       <c r="K12" s="208"/>
       <c r="L12" s="208"/>
-      <c r="M12" s="270"/>
+      <c r="M12" s="53"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -25963,19 +26070,19 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="197"/>
+      <c r="A13" s="640"/>
       <c r="B13" s="208"/>
       <c r="C13" s="208"/>
-      <c r="D13" s="212"/>
-      <c r="E13" s="213"/>
-      <c r="F13" s="214"/>
+      <c r="D13" s="645"/>
+      <c r="E13" s="646"/>
+      <c r="F13" s="647"/>
       <c r="G13" s="208"/>
       <c r="H13" s="215"/>
       <c r="I13" s="216"/>
       <c r="J13" s="215"/>
       <c r="K13" s="208"/>
       <c r="L13" s="208"/>
-      <c r="M13" s="232"/>
+      <c r="M13" s="64"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -25990,19 +26097,19 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="197"/>
+      <c r="A14" s="640"/>
       <c r="B14" s="208"/>
       <c r="C14" s="208"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="214"/>
+      <c r="D14" s="645"/>
+      <c r="E14" s="646"/>
+      <c r="F14" s="647"/>
       <c r="G14" s="203"/>
       <c r="H14" s="206"/>
       <c r="I14" s="271"/>
       <c r="J14" s="215"/>
       <c r="K14" s="203"/>
       <c r="L14" s="203"/>
-      <c r="M14" s="270"/>
+      <c r="M14" s="53"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -26017,19 +26124,19 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="197"/>
+      <c r="A15" s="640"/>
       <c r="B15" s="208"/>
       <c r="C15" s="208"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="213"/>
-      <c r="F15" s="214"/>
+      <c r="D15" s="645"/>
+      <c r="E15" s="646"/>
+      <c r="F15" s="647"/>
       <c r="G15" s="208"/>
       <c r="H15" s="215"/>
       <c r="I15" s="216"/>
       <c r="J15" s="215"/>
       <c r="K15" s="208"/>
       <c r="L15" s="208"/>
-      <c r="M15" s="270"/>
+      <c r="M15" s="53"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -26044,19 +26151,19 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="197"/>
+      <c r="A16" s="640"/>
       <c r="B16" s="208"/>
       <c r="C16" s="208"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="213"/>
-      <c r="F16" s="214"/>
+      <c r="D16" s="645"/>
+      <c r="E16" s="646"/>
+      <c r="F16" s="647"/>
       <c r="G16" s="208"/>
       <c r="H16" s="215"/>
       <c r="I16" s="216"/>
       <c r="J16" s="215"/>
       <c r="K16" s="208"/>
       <c r="L16" s="208"/>
-      <c r="M16" s="270"/>
+      <c r="M16" s="53"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -26071,19 +26178,19 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="197"/>
+      <c r="A17" s="640"/>
       <c r="B17" s="208"/>
       <c r="C17" s="208"/>
-      <c r="D17" s="212"/>
-      <c r="E17" s="213"/>
-      <c r="F17" s="214"/>
+      <c r="D17" s="645"/>
+      <c r="E17" s="646"/>
+      <c r="F17" s="647"/>
       <c r="G17" s="208"/>
       <c r="H17" s="215"/>
       <c r="I17" s="216"/>
       <c r="J17" s="215"/>
       <c r="K17" s="208"/>
       <c r="L17" s="208"/>
-      <c r="M17" s="270"/>
+      <c r="M17" s="53"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -26098,19 +26205,19 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="197"/>
+      <c r="A18" s="640"/>
       <c r="B18" s="208"/>
       <c r="C18" s="208"/>
-      <c r="D18" s="212"/>
-      <c r="E18" s="213"/>
-      <c r="F18" s="214"/>
+      <c r="D18" s="645"/>
+      <c r="E18" s="646"/>
+      <c r="F18" s="647"/>
       <c r="G18" s="208"/>
       <c r="H18" s="215"/>
       <c r="I18" s="216"/>
       <c r="J18" s="215"/>
       <c r="K18" s="208"/>
       <c r="L18" s="208"/>
-      <c r="M18" s="270"/>
+      <c r="M18" s="53"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -26125,19 +26232,19 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="211"/>
+      <c r="A19" s="644"/>
       <c r="B19" s="208"/>
       <c r="C19" s="208"/>
-      <c r="D19" s="212"/>
-      <c r="E19" s="213"/>
-      <c r="F19" s="214"/>
+      <c r="D19" s="645"/>
+      <c r="E19" s="646"/>
+      <c r="F19" s="647"/>
       <c r="G19" s="208"/>
       <c r="H19" s="215"/>
       <c r="I19" s="216"/>
       <c r="J19" s="215"/>
       <c r="K19" s="208"/>
       <c r="L19" s="208"/>
-      <c r="M19" s="270"/>
+      <c r="M19" s="53"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -26152,19 +26259,19 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="233"/>
+      <c r="A20" s="649"/>
       <c r="B20" s="234"/>
       <c r="C20" s="234"/>
-      <c r="D20" s="212"/>
-      <c r="E20" s="213"/>
-      <c r="F20" s="214"/>
+      <c r="D20" s="645"/>
+      <c r="E20" s="646"/>
+      <c r="F20" s="647"/>
       <c r="G20" s="208"/>
       <c r="H20" s="215"/>
       <c r="I20" s="216"/>
       <c r="J20" s="215"/>
       <c r="K20" s="208"/>
       <c r="L20" s="208"/>
-      <c r="M20" s="272"/>
+      <c r="M20" s="91"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -26179,19 +26286,19 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="233"/>
+      <c r="A21" s="649"/>
       <c r="B21" s="208"/>
       <c r="C21" s="208"/>
-      <c r="D21" s="212"/>
-      <c r="E21" s="213"/>
-      <c r="F21" s="214"/>
+      <c r="D21" s="645"/>
+      <c r="E21" s="646"/>
+      <c r="F21" s="647"/>
       <c r="G21" s="208"/>
       <c r="H21" s="215"/>
       <c r="I21" s="216"/>
       <c r="J21" s="215"/>
       <c r="K21" s="208"/>
       <c r="L21" s="208"/>
-      <c r="M21" s="272"/>
+      <c r="M21" s="91"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -26206,19 +26313,19 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="233"/>
+      <c r="A22" s="649"/>
       <c r="B22" s="234"/>
       <c r="C22" s="234"/>
-      <c r="D22" s="212"/>
-      <c r="E22" s="213"/>
-      <c r="F22" s="214"/>
+      <c r="D22" s="645"/>
+      <c r="E22" s="646"/>
+      <c r="F22" s="647"/>
       <c r="G22" s="208"/>
       <c r="H22" s="215"/>
       <c r="I22" s="216"/>
       <c r="J22" s="215"/>
       <c r="K22" s="208"/>
       <c r="L22" s="208"/>
-      <c r="M22" s="272"/>
+      <c r="M22" s="91"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -26233,19 +26340,19 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="211"/>
+      <c r="A23" s="644"/>
       <c r="B23" s="208"/>
       <c r="C23" s="208"/>
-      <c r="D23" s="212"/>
-      <c r="E23" s="213"/>
-      <c r="F23" s="214"/>
+      <c r="D23" s="645"/>
+      <c r="E23" s="646"/>
+      <c r="F23" s="647"/>
       <c r="G23" s="208"/>
       <c r="H23" s="215"/>
       <c r="I23" s="216"/>
       <c r="J23" s="215"/>
       <c r="K23" s="208"/>
       <c r="L23" s="208"/>
-      <c r="M23" s="270"/>
+      <c r="M23" s="53"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -26260,19 +26367,19 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24" ht="15.9" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="233"/>
+      <c r="A24" s="649"/>
       <c r="B24" s="234"/>
       <c r="C24" s="234"/>
-      <c r="D24" s="273"/>
-      <c r="E24" s="274"/>
-      <c r="F24" s="275"/>
+      <c r="D24" s="650"/>
+      <c r="E24" s="651"/>
+      <c r="F24" s="652"/>
       <c r="G24" s="234"/>
       <c r="H24" s="235"/>
       <c r="I24" s="276"/>
       <c r="J24" s="235"/>
       <c r="K24" s="234"/>
       <c r="L24" s="234"/>
-      <c r="M24" s="272"/>
+      <c r="M24" s="91"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -26894,7 +27001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -27624,7 +27731,7 @@
       <c r="A6" s="188" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="190" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -27636,7 +27743,7 @@
       <c r="I6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="639"/>
       <c r="K6" s="3" t="str">
         <f>'OS-IN'!H6</f>
         <v>0148N</v>
@@ -27692,7 +27799,7 @@
       <c r="A8" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="188" t="s">
+      <c r="B8" s="190" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="188"/>
@@ -27753,7 +27860,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="191" t="s">
         <v>11</v>
       </c>
@@ -27794,7 +27901,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="194"/>
       <c r="B11" s="194"/>
       <c r="C11" s="249"/>
@@ -28604,7 +28711,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -29396,7 +29503,7 @@
       <c r="A6" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="653" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="40"/>
@@ -29464,20 +29571,20 @@
       <c r="A8" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="40"/>
+      <c r="B8" s="653"/>
       <c r="C8" s="241"/>
       <c r="D8" s="241"/>
       <c r="E8" s="241"/>
       <c r="F8" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="40"/>
+      <c r="G8" s="653"/>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
       <c r="J8" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="K8" s="145" t="s">
+      <c r="K8" s="654" t="s">
         <v>14</v>
       </c>
       <c r="L8" s="145" t="s">
@@ -29504,7 +29611,7 @@
         <v>88</v>
       </c>
       <c r="B9" s="241"/>
-      <c r="C9" s="40"/>
+      <c r="C9" s="653"/>
       <c r="D9" s="40"/>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
@@ -30157,7 +30264,7 @@
       </c>
       <c r="B33" s="296"/>
       <c r="C33" s="296"/>
-      <c r="D33" s="297"/>
+      <c r="D33" s="655"/>
       <c r="E33" s="297"/>
       <c r="F33" s="297"/>
       <c r="G33" s="297"/>
@@ -30853,7 +30960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -31520,9 +31627,7 @@
       <c r="Y3" s="3"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="188" t="s">
-        <v>121</v>
-      </c>
+      <c r="A4" s="188"/>
       <c r="B4" s="188"/>
       <c r="C4" s="188"/>
       <c r="D4" s="188"/>
@@ -31530,7 +31635,7 @@
       <c r="F4" s="317" t="s">
         <v>122</v>
       </c>
-      <c r="G4" s="189"/>
+      <c r="G4" s="638"/>
       <c r="H4" s="175"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -31581,7 +31686,7 @@
       <c r="A6" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="639"/>
       <c r="C6" s="3" t="str">
         <f>'OS-IN'!H6</f>
         <v>0148N</v>
@@ -31593,7 +31698,7 @@
       <c r="F6" s="317" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="316" t="s">
+      <c r="G6" s="656" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="3"/>
@@ -32236,12 +32341,12 @@
     <row r="29" ht="23.1" customHeight="1" spans="1:25" s="323" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="342"/>
       <c r="B29" s="343"/>
-      <c r="C29" s="363"/>
-      <c r="D29" s="363"/>
-      <c r="E29" s="363"/>
-      <c r="F29" s="363"/>
-      <c r="G29" s="363"/>
-      <c r="H29" s="364"/>
+      <c r="C29" s="657"/>
+      <c r="D29" s="657"/>
+      <c r="E29" s="657"/>
+      <c r="F29" s="657"/>
+      <c r="G29" s="657"/>
+      <c r="H29" s="658"/>
       <c r="I29" s="323"/>
       <c r="J29" s="323"/>
       <c r="K29" s="323"/>
@@ -32263,12 +32368,12 @@
     <row r="30" ht="23.1" customHeight="1" spans="1:25" s="323" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="342"/>
       <c r="B30" s="343"/>
-      <c r="C30" s="363"/>
-      <c r="D30" s="363"/>
-      <c r="E30" s="363"/>
-      <c r="F30" s="363"/>
-      <c r="G30" s="363"/>
-      <c r="H30" s="364"/>
+      <c r="C30" s="657"/>
+      <c r="D30" s="657"/>
+      <c r="E30" s="657"/>
+      <c r="F30" s="657"/>
+      <c r="G30" s="657"/>
+      <c r="H30" s="658"/>
       <c r="I30" s="323"/>
       <c r="J30" s="323"/>
       <c r="K30" s="323"/>
@@ -32290,12 +32395,12 @@
     <row r="31" ht="23.1" customHeight="1" spans="1:25" s="323" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="347"/>
       <c r="B31" s="348"/>
-      <c r="C31" s="365"/>
-      <c r="D31" s="365"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
-      <c r="G31" s="365"/>
-      <c r="H31" s="366"/>
+      <c r="C31" s="659"/>
+      <c r="D31" s="659"/>
+      <c r="E31" s="659"/>
+      <c r="F31" s="659"/>
+      <c r="G31" s="659"/>
+      <c r="H31" s="660"/>
       <c r="I31" s="323"/>
       <c r="J31" s="323"/>
       <c r="K31" s="323"/>
@@ -32581,9 +32686,7 @@
       <c r="Y40" s="3"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="188" t="s">
-        <v>138</v>
-      </c>
+      <c r="A41" s="188"/>
       <c r="B41" s="188"/>
       <c r="C41" s="188"/>
       <c r="D41" s="188"/>
@@ -32645,7 +32748,7 @@
       <c r="A43" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B43" s="3"/>
+      <c r="B43" s="639"/>
       <c r="C43" s="3" t="str">
         <f>'OS-OUT'!H6</f>
         <v>0149S</v>
@@ -32657,7 +32760,7 @@
       <c r="F43" s="317" t="s">
         <v>124</v>
       </c>
-      <c r="G43" s="316" t="s">
+      <c r="G43" s="656" t="s">
         <v>26</v>
       </c>
       <c r="H43" s="3"/>
